--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,6 +912,1671 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129196452</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78792</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>466732</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6858915</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129196437</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>466811</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6858835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129196570</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466785</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6858943</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129196552</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466767</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6858965</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129196558</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>466772</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6858948</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129196477</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466786</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6858845</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129196601</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466798</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6858935</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129196521</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6858870</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129197438</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79625</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466756</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6858862</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129196486</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6858909</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129196613</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>185</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466805</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6858943</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129196622</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>185</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>466818</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6858937</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129196445</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78792</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>466788</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6858852</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129197446</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78701</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>466756</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6858862</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129196626</v>
+      </c>
+      <c r="B18" t="n">
+        <v>81020</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466807</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6858944</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78793</v>
+        <v>79067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79067</v>
+        <v>78793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>78701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R16" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78701</v>
+        <v>78792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R17" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129196452</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129196437</v>
       </c>
       <c r="B5" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129196570</v>
       </c>
       <c r="B6" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129196552</v>
       </c>
       <c r="B7" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129196558</v>
       </c>
       <c r="B8" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79067</v>
+        <v>78797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78793</v>
+        <v>79071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R11" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B12" t="n">
-        <v>79625</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R12" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1917,7 @@
         <v>129196486</v>
       </c>
       <c r="B13" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129196613</v>
       </c>
       <c r="B14" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129196622</v>
       </c>
       <c r="B15" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>129196626</v>
       </c>
       <c r="B18" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78797</v>
+        <v>79071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79071</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R11" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R12" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B16" t="n">
-        <v>78705</v>
+        <v>78796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R16" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B17" t="n">
-        <v>78796</v>
+        <v>78705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R17" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129196452</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129196437</v>
       </c>
       <c r="B5" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129196570</v>
       </c>
       <c r="B6" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129196552</v>
       </c>
       <c r="B7" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129196558</v>
       </c>
       <c r="B8" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79071</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R11" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R12" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1917,7 @@
         <v>129196486</v>
       </c>
       <c r="B13" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129196613</v>
       </c>
       <c r="B14" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129196622</v>
       </c>
       <c r="B15" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78796</v>
+        <v>78707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R16" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78705</v>
+        <v>78798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R17" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,7 +2472,7 @@
         <v>129196626</v>
       </c>
       <c r="B18" t="n">
-        <v>81024</v>
+        <v>81026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>79073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R11" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R12" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B16" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R16" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R17" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2578,6 +2578,103 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129382885</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78799</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>466572</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6858763</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>79073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R11" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B12" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R12" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R11" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R12" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R16" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R17" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129196452</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129196437</v>
       </c>
       <c r="B5" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129196570</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129196552</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129196558</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129196486</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129196613</v>
       </c>
       <c r="B14" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129196622</v>
       </c>
       <c r="B15" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>129196626</v>
       </c>
       <c r="B18" t="n">
-        <v>81026</v>
+        <v>81028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129196452</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129196437</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129196570</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129196552</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129196558</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129196486</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129196613</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129196622</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B16" t="n">
-        <v>78709</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R16" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B17" t="n">
-        <v>78800</v>
+        <v>78710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R17" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,7 +2472,7 @@
         <v>129196626</v>
       </c>
       <c r="B18" t="n">
-        <v>81028</v>
+        <v>81029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R16" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R17" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R16" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R17" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129196445</v>
+        <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466788</v>
+        <v>466756</v>
       </c>
       <c r="R16" t="n">
-        <v>6858852</v>
+        <v>6858862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129197446</v>
+        <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466756</v>
+        <v>466788</v>
       </c>
       <c r="R17" t="n">
-        <v>6858862</v>
+        <v>6858852</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,22 +2426,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,6 +2675,394 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129604003</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>466498</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6858702</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129604024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>466487</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6858709</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129604483</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>466647</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6858779</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129603921</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>466452</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6858667</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129196552</v>
+        <v>129196558</v>
       </c>
       <c r="B7" t="n">
         <v>79076</v>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466767</v>
+        <v>466772</v>
       </c>
       <c r="R7" t="n">
-        <v>6858965</v>
+        <v>6858948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129196558</v>
+        <v>129196552</v>
       </c>
       <c r="B8" t="n">
         <v>79076</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466772</v>
+        <v>466767</v>
       </c>
       <c r="R8" t="n">
-        <v>6858948</v>
+        <v>6858965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129196558</v>
+        <v>129196552</v>
       </c>
       <c r="B7" t="n">
         <v>79076</v>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466772</v>
+        <v>466767</v>
       </c>
       <c r="R7" t="n">
-        <v>6858948</v>
+        <v>6858965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129196552</v>
+        <v>129196558</v>
       </c>
       <c r="B8" t="n">
         <v>79076</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466767</v>
+        <v>466772</v>
       </c>
       <c r="R8" t="n">
-        <v>6858965</v>
+        <v>6858948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R11" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B12" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R12" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3063,6 +3063,713 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129649793</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>466488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6858709</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129649820</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129649815</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78447</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129649813</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78052</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129649822</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>466566</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6858765</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129649784</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80178</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>466488</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6858709</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129649789</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>466488</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6858709</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R9" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R10" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R11" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R12" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129174947</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129174959</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129196452</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129196437</v>
       </c>
       <c r="B5" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129196570</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129196552</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129196558</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129196477</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>129196601</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R11" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B12" t="n">
-        <v>79634</v>
+        <v>79689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R12" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1917,7 @@
         <v>129196486</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>129196613</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129196622</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>129197446</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129196445</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>129196626</v>
       </c>
       <c r="B18" t="n">
-        <v>81029</v>
+        <v>81055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78052</v>
+        <v>78078</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129196477</v>
+        <v>129196601</v>
       </c>
       <c r="B9" t="n">
-        <v>78828</v>
+        <v>79102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466786</v>
+        <v>466798</v>
       </c>
       <c r="R9" t="n">
-        <v>6858845</v>
+        <v>6858935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129196601</v>
+        <v>129196477</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
+        <v>78828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466798</v>
+        <v>466786</v>
       </c>
       <c r="R10" t="n">
-        <v>6858935</v>
+        <v>6858845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129197438</v>
+        <v>129196521</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466756</v>
+        <v>466759</v>
       </c>
       <c r="R11" t="n">
-        <v>6858862</v>
+        <v>6858870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129196521</v>
+        <v>129197438</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466759</v>
+        <v>466756</v>
       </c>
       <c r="R12" t="n">
-        <v>6858870</v>
+        <v>6858862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,22 +1871,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78078</v>
+        <v>78083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78083</v>
+        <v>78084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>129382885</v>
       </c>
       <c r="B19" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>78487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78089</v>
+        <v>78092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -2680,7 +2680,7 @@
         <v>129604003</v>
       </c>
       <c r="B20" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>129604024</v>
       </c>
       <c r="B21" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129604483</v>
       </c>
       <c r="B22" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129603921</v>
       </c>
       <c r="B23" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78487</v>
+        <v>78490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>129649813</v>
       </c>
       <c r="B27" t="n">
-        <v>78092</v>
+        <v>78095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 31911-2025 artfynd.xlsx
+++ b/artfynd/A 31911-2025 artfynd.xlsx
@@ -3068,7 +3068,7 @@
         <v>129649793</v>
       </c>
       <c r="B24" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>129649820</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>129649815</v>
       </c>
       <c r="B26" t="n">
-        <v>78490</v>
+        <v>78491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129649822</v>
       </c>
       <c r="B28" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>129649784</v>
       </c>
       <c r="B29" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129649789</v>
       </c>
       <c r="B30" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
